--- a/Format_cell.xlsx
+++ b/Format_cell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dmart_Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{085D7CBD-76D0-4005-BA2D-6F4817601BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA83F30-C1B3-4057-8BA9-D81CBCB04CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{69532D2C-0067-4794-AFF4-1A8228E90DD3}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>NAME</t>
   </si>
@@ -101,6 +101,15 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>MARK</t>
+  </si>
+  <si>
+    <t>GRADE</t>
+  </si>
+  <si>
+    <t>IF ERROR</t>
   </si>
 </sst>
 </file>
@@ -123,7 +132,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +142,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -149,18 +164,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="2">
     <dxf>
       <font>
         <b/>
@@ -170,44 +189,6 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FF00B050"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.89996032593768116"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -612,7 +593,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E7">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -755,10 +736,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C248CF-9393-4BB3-B323-D5A83E17E6F9}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -768,8 +749,21 @@
       <c r="C1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -779,8 +773,30 @@
       <c r="C2">
         <v>4000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="5">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="str">
+        <f t="shared" ref="G2:G7" si="0">IF(F2&gt;40,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+      <c r="H2" s="5" t="str">
+        <f>IF(F2&gt;70,"A",IF(F2&gt;60,"B","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+      <c r="I2" s="5" t="str">
+        <f>IFERROR(IF(F2&gt;70,"A",IF(F2&gt;60,"B",IF(F2&gt;30,"C","FAIL"))),"INVALID")</f>
+        <v>FAIL</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="4"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -790,8 +806,32 @@
       <c r="C3">
         <v>6000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5">
+        <v>68</v>
+      </c>
+      <c r="G3" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f t="shared" ref="H3:H7" si="1">IF(F3&gt;70,"A",IF(F3&gt;60,"B","FAIL"))</f>
+        <v>B</v>
+      </c>
+      <c r="I3" s="5" t="str">
+        <f t="shared" ref="I3:I7" si="2">IFERROR(IF(F3&gt;70,"A",IF(F3&gt;60,"B",IF(F3&gt;30,"C","FAIL"))),"INVALID")</f>
+        <v>B</v>
+      </c>
+      <c r="K3">
+        <v>30</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -801,8 +841,31 @@
       <c r="C4">
         <v>5400</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5">
+        <v>65</v>
+      </c>
+      <c r="G4" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H4" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>B</v>
+      </c>
+      <c r="I4" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>B</v>
+      </c>
+      <c r="K4" s="4" t="str">
+        <f>IFERROR(K3/L3,"Cant Divide")</f>
+        <v>Cant Divide</v>
+      </c>
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -812,8 +875,26 @@
       <c r="C5">
         <v>2500</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="E5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="5">
+        <v>35</v>
+      </c>
+      <c r="G5" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>FAIL</v>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>FAIL</v>
+      </c>
+      <c r="I5" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>C</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -823,11 +904,43 @@
       <c r="C6">
         <v>8000</v>
       </c>
+      <c r="E6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5">
+        <v>87</v>
+      </c>
+      <c r="G6" s="5" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+      <c r="H6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>A</v>
+      </c>
+      <c r="I6" s="5" t="str">
+        <f t="shared" si="2"/>
+        <v>A</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:C6">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <mergeCells count="2">
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K2:L2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:C6 E1:H1">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$C2&gt;$B2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FF92D050"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
